--- a/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
@@ -649,10 +649,10 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -835,10 +835,10 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1015,10 +1015,10 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4">
         <v>0</v>

--- a/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="45">
   <si>
     <t>Mat</t>
   </si>
@@ -88,121 +88,70 @@
     <t>FLORES</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>LUCIANO</t>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>-------------</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
+    <t>SUAREZ</t>
   </si>
   <si>
     <t>AUTRAN</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
     <t>NATANAHEL</t>
   </si>
   <si>
-    <t>ROBBIE ALONSO</t>
-  </si>
-  <si>
-    <t>ILIAN ANELI</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>URIEL</t>
+    <t>MICHEL LEONEL</t>
   </si>
   <si>
     <t>JESHUA</t>
   </si>
   <si>
-    <t>CLARA LIZBETH</t>
-  </si>
-  <si>
-    <t>HEIDI KESEI</t>
-  </si>
-  <si>
-    <t>JULIO ALBERTO</t>
-  </si>
-  <si>
-    <t>XOCHITL ALELI</t>
-  </si>
-  <si>
-    <t>YUREN</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>ESTEBAN</t>
+    <t>AARON</t>
+  </si>
+  <si>
+    <t>SERGIO JOSUE</t>
+  </si>
+  <si>
+    <t>ELI ANTONIO</t>
   </si>
   <si>
     <t>AXEL AARON</t>
   </si>
   <si>
-    <t>KEVYN DANIEL</t>
+    <t>DULIAM</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
   </si>
 </sst>
 </file>
@@ -603,10 +552,10 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2">
         <v>12</v>
@@ -629,16 +578,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>43.24</v>
+      </c>
+      <c r="H3">
+        <v>5.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -652,16 +604,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>73.68000000000001</v>
+      </c>
+      <c r="H4">
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -792,16 +747,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>36.11</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -815,16 +773,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>37.84</v>
+      </c>
+      <c r="H3">
+        <v>5.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -838,16 +799,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>68.42</v>
+      </c>
+      <c r="H4">
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -861,16 +825,19 @@
         <v>28</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>78.56999999999999</v>
+      </c>
+      <c r="H5">
+        <v>6.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -884,16 +851,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>89.29000000000001</v>
+      </c>
+      <c r="H6">
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -907,16 +877,19 @@
         <v>28</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>89.29000000000001</v>
+      </c>
+      <c r="H7">
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -969,19 +942,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>23</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>33.33</v>
+        <v>36.11</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -995,16 +968,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>37.84</v>
+      </c>
+      <c r="H3">
+        <v>5.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1018,16 +994,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>68.42</v>
+      </c>
+      <c r="H4">
+        <v>6.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1053,7 +1032,7 @@
         <v>78.56999999999999</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1070,13 +1049,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>85.70999999999999</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H6">
         <v>7.5</v>
@@ -1096,16 +1075,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G7">
-        <v>92.86</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1115,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1153,10 +1132,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1170,22 +1149,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920204</v>
+        <v>23330051920299</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1193,16 +1172,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920322</v>
+        <v>23330051920310</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1216,16 +1195,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920296</v>
+        <v>23330051920363</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1239,22 +1218,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920297</v>
+        <v>23330051920332</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1262,22 +1241,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920310</v>
+        <v>20330051920366</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1285,208 +1264,93 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920287</v>
+        <v>23330051920190</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920288</v>
+        <v>20330051920078</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920290</v>
+        <v>21330051920012</v>
       </c>
       <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920325</v>
+        <v>20330051920367</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920331</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920304</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920305</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920190</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920192</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
@@ -97,7 +97,10 @@
     <t>ROMERO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>NAJERA</t>
@@ -106,7 +109,7 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>AUTRAN</t>
   </si>
   <si>
     <t>GUEVARA</t>
@@ -118,10 +121,10 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>AUTRAN</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>AXEL AARON</t>
   </si>
   <si>
     <t>NATANAHEL</t>
@@ -136,19 +139,16 @@
     <t>AARON</t>
   </si>
   <si>
-    <t>SERGIO JOSUE</t>
+    <t>HUGO ANTONIO</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
   </si>
   <si>
     <t>ELI ANTONIO</t>
   </si>
   <si>
-    <t>AXEL AARON</t>
-  </si>
-  <si>
     <t>DULIAM</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
   </si>
   <si>
     <t>ISAAC</t>
@@ -747,7 +747,7 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>23</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920189</v>
+        <v>23330051920190</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -1149,13 +1149,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920299</v>
+        <v>23330051920189</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
         <v>36</v>
@@ -1164,7 +1164,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1172,13 +1172,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920310</v>
+        <v>23330051920299</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
         <v>37</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920363</v>
+        <v>23330051920310</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920332</v>
+        <v>23330051920363</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
         <v>33</v>
@@ -1233,7 +1233,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1241,22 +1241,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920366</v>
+        <v>23330051920311</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
         <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1264,36 +1264,36 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920190</v>
+        <v>21330051920012</v>
       </c>
       <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
         <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
       </c>
       <c r="D8" t="s">
         <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920078</v>
+        <v>20330051920366</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
@@ -1305,12 +1305,12 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920012</v>
+        <v>20330051920078</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
@@ -1322,7 +1322,7 @@
         <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>15</v>
@@ -1336,10 +1336,10 @@
         <v>20330051920367</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
         <v>44</v>

--- a/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="65">
   <si>
     <t>Mat</t>
   </si>
@@ -85,9 +85,36 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>AVILA</t>
+  </si>
+  <si>
+    <t>BERTELY</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
@@ -97,39 +124,78 @@
     <t>ROMERO</t>
   </si>
   <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
   </si>
   <si>
     <t>AUTRAN</t>
   </si>
   <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
     <t>GUEVARA</t>
   </si>
   <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
   </si>
   <si>
     <t>AXEL AARON</t>
   </si>
   <si>
+    <t>MARIANA JANET</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>DANIEL DE JESUS</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
     <t>NATANAHEL</t>
   </si>
   <si>
+    <t>ROBBIE ALONSO</t>
+  </si>
+  <si>
+    <t>JURISEL</t>
+  </si>
+  <si>
     <t>MICHEL LEONEL</t>
   </si>
   <si>
@@ -139,16 +205,10 @@
     <t>AARON</t>
   </si>
   <si>
-    <t>HUGO ANTONIO</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
+    <t>DULIAM</t>
   </si>
   <si>
     <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
   </si>
   <si>
     <t>ISAAC</t>
@@ -1094,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1126,16 +1186,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920190</v>
+        <v>23330051920183</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1149,16 +1209,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920189</v>
+        <v>23330051920184</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1172,22 +1232,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920299</v>
+        <v>23330051920190</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1195,16 +1255,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920310</v>
+        <v>23330051920282</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1218,16 +1278,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920363</v>
+        <v>23330051920284</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1241,16 +1301,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920311</v>
+        <v>23330051920285</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1267,13 +1327,13 @@
         <v>21330051920012</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
@@ -1287,45 +1347,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920366</v>
+        <v>23330051920185</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920078</v>
+        <v>23330051920189</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1333,24 +1393,185 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
+        <v>23330051920204</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920281</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920299</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920310</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920363</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920078</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920366</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
         <v>20330051920367</v>
       </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" t="s">
         <v>9</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F18" t="s">
         <v>15</v>
       </c>
-      <c r="G11">
+      <c r="G18">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="70">
   <si>
     <t>Mat</t>
   </si>
@@ -88,63 +88,75 @@
     <t>CHICO</t>
   </si>
   <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>NARVAEZ</t>
+  </si>
+  <si>
+    <t>AVILA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
     <t>CORDOVA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>AVILA</t>
-  </si>
-  <si>
-    <t>BERTELY</t>
-  </si>
-  <si>
-    <t>CORTES</t>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>AUTRAN</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>AUTRAN</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
     <t>COCOTLE</t>
   </si>
   <si>
@@ -154,9 +166,6 @@
     <t>SOLANO</t>
   </si>
   <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
     <t>HERRERA</t>
   </si>
   <si>
@@ -166,52 +175,58 @@
     <t>FERNANDO</t>
   </si>
   <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>AXEL AARON</t>
+  </si>
+  <si>
+    <t>ARMANDO GABRIEL</t>
+  </si>
+  <si>
+    <t>LAZARO</t>
+  </si>
+  <si>
+    <t>MARIANA JANET</t>
+  </si>
+  <si>
+    <t>DANIEL DE JESUS</t>
+  </si>
+  <si>
+    <t>SERGIO JOSUE</t>
+  </si>
+  <si>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
     <t>CRISTOPHER</t>
   </si>
   <si>
-    <t>AXEL AARON</t>
-  </si>
-  <si>
-    <t>MARIANA JANET</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>DANIEL DE JESUS</t>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>ROBBIE ALONSO</t>
+  </si>
+  <si>
+    <t>MICHEL LEONEL</t>
+  </si>
+  <si>
+    <t>JESHUA</t>
+  </si>
+  <si>
+    <t>AARON</t>
+  </si>
+  <si>
+    <t>DULIAM</t>
   </si>
   <si>
     <t>ARIEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
-    <t>ROBBIE ALONSO</t>
-  </si>
-  <si>
-    <t>JURISEL</t>
-  </si>
-  <si>
-    <t>MICHEL LEONEL</t>
-  </si>
-  <si>
-    <t>JESHUA</t>
-  </si>
-  <si>
-    <t>AARON</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
   </si>
 </sst>
 </file>
@@ -1005,16 +1020,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>36.11</v>
+        <v>33.33</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1031,16 +1046,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>37.84</v>
+        <v>51.35</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1066,7 +1081,7 @@
         <v>68.42</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1154,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1192,10 +1207,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1209,16 +1224,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920184</v>
+        <v>23330051920188</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1238,10 +1253,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1255,22 +1270,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920282</v>
+        <v>23330051920324</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1278,22 +1293,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920284</v>
+        <v>23330051920202</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1301,16 +1316,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920285</v>
+        <v>23330051920282</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1324,22 +1339,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920012</v>
+        <v>23330051920285</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1347,76 +1362,76 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920185</v>
+        <v>23330051920332</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920189</v>
+        <v>20330051920366</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920204</v>
+        <v>20330051920367</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920281</v>
+        <v>23330051920184</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -1425,13 +1440,13 @@
         <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1439,22 +1454,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920299</v>
+        <v>23330051920185</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1462,22 +1477,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920310</v>
+        <v>23330051920189</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1485,22 +1500,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920363</v>
+        <v>23330051920204</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1508,22 +1523,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920078</v>
+        <v>23330051920299</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1531,22 +1546,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920366</v>
+        <v>23330051920310</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1554,24 +1569,70 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920367</v>
+        <v>23330051920363</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920078</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" t="s">
         <v>9</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F19" t="s">
         <v>15</v>
       </c>
-      <c r="G18">
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920012</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="65">
   <si>
     <t>Mat</t>
   </si>
@@ -94,9 +94,6 @@
     <t>FLORES</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
     <t>NARVAEZ</t>
   </si>
   <si>
@@ -130,42 +127,39 @@
     <t>ROMERO</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>AUTRAN</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>AUTRAN</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
     <t>HERRERA</t>
   </si>
   <si>
@@ -181,9 +175,6 @@
     <t>AXEL AARON</t>
   </si>
   <si>
-    <t>ARMANDO GABRIEL</t>
-  </si>
-  <si>
     <t>LAZARO</t>
   </si>
   <si>
@@ -221,12 +212,6 @@
   </si>
   <si>
     <t>AARON</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
   </si>
 </sst>
 </file>
@@ -1098,16 +1083,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>78.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1124,16 +1109,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>89.29000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1150,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>89.29000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -1169,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1207,10 +1192,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1230,10 +1215,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1253,10 +1238,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1270,16 +1255,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920324</v>
+        <v>23330051920202</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1293,22 +1278,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920202</v>
+        <v>23330051920282</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1316,16 +1301,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920282</v>
+        <v>23330051920285</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1339,22 +1324,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920285</v>
+        <v>23330051920332</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1362,22 +1347,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920332</v>
+        <v>20330051920366</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1385,16 +1370,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920366</v>
+        <v>20330051920367</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1408,39 +1393,39 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920367</v>
+        <v>23330051920184</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920184</v>
+        <v>23330051920185</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1454,16 +1439,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920185</v>
+        <v>23330051920189</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1477,16 +1462,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920189</v>
+        <v>23330051920204</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1500,22 +1485,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920204</v>
+        <v>23330051920299</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1523,16 +1508,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920299</v>
+        <v>23330051920310</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1546,16 +1531,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920310</v>
+        <v>23330051920363</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1564,75 +1549,6 @@
         <v>13</v>
       </c>
       <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920363</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920078</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920012</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
@@ -97,36 +97,36 @@
     <t>NARVAEZ</t>
   </si>
   <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>AVILA</t>
   </si>
   <si>
     <t>CORTES</t>
   </si>
   <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
@@ -136,36 +136,36 @@
     <t>AUTRAN</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
     <t>PABLO</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>SUAREZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>FERNANDO</t>
   </si>
   <si>
@@ -178,40 +178,40 @@
     <t>LAZARO</t>
   </si>
   <si>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>ROBBIE ALONSO</t>
+  </si>
+  <si>
     <t>MARIANA JANET</t>
   </si>
   <si>
     <t>DANIEL DE JESUS</t>
   </si>
   <si>
+    <t>MICHEL LEONEL</t>
+  </si>
+  <si>
+    <t>JESHUA</t>
+  </si>
+  <si>
+    <t>AARON</t>
+  </si>
+  <si>
     <t>SERGIO JOSUE</t>
-  </si>
-  <si>
-    <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
-    <t>ROBBIE ALONSO</t>
-  </si>
-  <si>
-    <t>MICHEL LEONEL</t>
-  </si>
-  <si>
-    <t>JESHUA</t>
-  </si>
-  <si>
-    <t>AARON</t>
   </si>
 </sst>
 </file>
@@ -1261,7 +1261,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
         <v>52</v>
@@ -1278,7 +1278,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920282</v>
+        <v>20330051920366</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1290,10 +1290,10 @@
         <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920285</v>
+        <v>20330051920367</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
         <v>54</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920332</v>
+        <v>23330051920184</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
         <v>40</v>
@@ -1339,18 +1339,18 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920366</v>
+        <v>23330051920185</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>41</v>
@@ -1359,47 +1359,47 @@
         <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920367</v>
+        <v>23330051920189</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920184</v>
+        <v>23330051920204</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
         <v>58</v>
@@ -1416,13 +1416,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920185</v>
+        <v>23330051920282</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
         <v>59</v>
@@ -1431,7 +1431,7 @@
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1439,13 +1439,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920189</v>
+        <v>23330051920285</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
         <v>60</v>
@@ -1454,7 +1454,7 @@
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920204</v>
+        <v>23330051920299</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
@@ -1477,7 +1477,7 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920299</v>
+        <v>23330051920310</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920310</v>
+        <v>23330051920363</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920363</v>
+        <v>23330051920332</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
@@ -1546,7 +1546,7 @@
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17">
         <v>1</v>

--- a/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
@@ -1014,7 +1014,7 @@
         <v>33.33</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1040,7 +1040,7 @@
         <v>51.35</v>
       </c>
       <c r="H3">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1066,7 +1066,7 @@
         <v>68.42</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1092,7 +1092,7 @@
         <v>85.70999999999999</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1118,7 +1118,7 @@
         <v>92.86</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1144,7 +1144,7 @@
         <v>92.86</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="68">
   <si>
     <t>Mat</t>
   </si>
@@ -97,6 +97,9 @@
     <t>NARVAEZ</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>NAJERA</t>
   </si>
   <si>
@@ -136,6 +139,9 @@
     <t>AUTRAN</t>
   </si>
   <si>
+    <t>VILLA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -176,6 +182,9 @@
   </si>
   <si>
     <t>LAZARO</t>
+  </si>
+  <si>
+    <t>ALEX URIEL</t>
   </si>
   <si>
     <t>ELI ANTONIO</t>
@@ -1014,7 +1023,7 @@
         <v>33.33</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1040,7 +1049,7 @@
         <v>51.35</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1066,7 +1075,7 @@
         <v>68.42</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1092,7 +1101,7 @@
         <v>85.70999999999999</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1118,7 +1127,7 @@
         <v>92.86</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1144,7 +1153,7 @@
         <v>92.86</v>
       </c>
       <c r="H7">
-        <v>9.6</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -1154,7 +1163,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1192,10 +1201,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1215,10 +1224,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1238,10 +1247,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1261,10 +1270,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1278,22 +1287,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920366</v>
+        <v>23330051920212</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1301,16 +1310,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920367</v>
+        <v>20330051920366</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1324,39 +1333,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920184</v>
+        <v>20330051920367</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920185</v>
+        <v>23330051920184</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1370,16 +1379,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920189</v>
+        <v>23330051920185</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1393,16 +1402,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920204</v>
+        <v>23330051920189</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1416,22 +1425,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920282</v>
+        <v>23330051920204</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1439,16 +1448,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920285</v>
+        <v>23330051920282</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1462,16 +1471,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920299</v>
+        <v>23330051920285</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1485,16 +1494,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920310</v>
+        <v>23330051920299</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1508,16 +1517,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920363</v>
+        <v>23330051920310</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1531,24 +1540,47 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920332</v>
+        <v>23330051920363</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920332</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
         <v>14</v>
       </c>
-      <c r="G17">
+      <c r="G18">
         <v>1</v>
       </c>
     </row>
